--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20232.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20232.xlsx
@@ -85,37 +85,37 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>CAMARILLO</t>
   </si>
   <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>CORRO</t>
+  </si>
+  <si>
     <t>SUAREZ</t>
   </si>
   <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>TETLA</t>
+    <t>JIMENEZ</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>EVANGELISTA</t>
   </si>
   <si>
-    <t>XOCHITL ALELI</t>
-  </si>
-  <si>
-    <t>HECTOR</t>
+    <t>MIGUEL ANGEL</t>
   </si>
   <si>
     <t>DIEGO</t>
+  </si>
+  <si>
+    <t>DINORAH AZUL</t>
   </si>
   <si>
     <t>SAUL KOURCHENKOV</t>
@@ -662,16 +662,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80.65000000000001</v>
+      </c>
+      <c r="H2">
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -685,16 +688,19 @@
         <v>12</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H3">
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -708,16 +714,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H4">
+        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -731,16 +740,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>95.83</v>
+      </c>
+      <c r="H5">
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -796,16 +808,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>64.52</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -831,7 +843,7 @@
         <v>75</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -857,7 +869,7 @@
         <v>80</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -874,16 +886,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>91.67</v>
+        <v>95.83</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +937,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920325</v>
+        <v>22330051920153</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -937,10 +949,10 @@
         <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -948,7 +960,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920160</v>
+        <v>21330051920112</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -960,10 +972,10 @@
         <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -971,7 +983,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920112</v>
+        <v>22330051920162</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20232.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,42 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CORRO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>DINORAH AZUL</t>
-  </si>
-  <si>
-    <t>SAUL KOURCHENKOV</t>
   </si>
 </sst>
 </file>
@@ -808,16 +772,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>80.65000000000001</v>
+        <v>93.55</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -843,7 +807,7 @@
         <v>75</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -860,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>80</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H4">
         <v>7.7</v>
@@ -895,7 +859,7 @@
         <v>95.83</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -905,7 +869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -935,98 +899,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920153</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920112</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920162</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920282</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
